--- a/data/trans_camb/IP04D$individual-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Edad-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 5,57</t>
+          <t>-10,9; 6,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,71; -0,96</t>
+          <t>-20,01; -0,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -0,19</t>
+          <t>-18,31; -0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,12; -2,18</t>
+          <t>-24,74; -3,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,03; -0,46</t>
+          <t>-12,58; 0,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,54; -4,5</t>
+          <t>-19,53; -4,75</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 23,49</t>
+          <t>-34,02; 24,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,59; -3,51</t>
+          <t>-63,38; -0,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 0,76</t>
+          <t>-43,54; -2,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,38; -5,87</t>
+          <t>-58,45; -8,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,94; -0,65</t>
+          <t>-34,4; 1,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,55; -15,36</t>
+          <t>-54,13; -15,37</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 16,52</t>
+          <t>2,68; 17,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -2,82</t>
+          <t>-17,0; -3,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 7,47</t>
+          <t>-5,08; 8,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -3,11</t>
+          <t>-16,71; -3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 9,99</t>
+          <t>0,98; 10,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,99; -5,16</t>
+          <t>-15,35; -5,44</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 70,84</t>
+          <t>8,43; 71,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,73; -11,3</t>
+          <t>-56,73; -14,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 30,81</t>
+          <t>-16,97; 36,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,35; -11,82</t>
+          <t>-55,51; -12,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 39,23</t>
+          <t>3,29; 41,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,63; -20,67</t>
+          <t>-51,28; -21,66</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 7,92</t>
+          <t>-9,6; 6,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,23; -8,53</t>
+          <t>-24,74; -8,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 5,03</t>
+          <t>-12,93; 3,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,0; -4,76</t>
+          <t>-20,47; -4,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 3,36</t>
+          <t>-8,11; 3,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -8,26</t>
+          <t>-20,21; -8,65</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 31,24</t>
+          <t>-27,1; 26,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,99; -30,35</t>
+          <t>-68,45; -31,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 15,48</t>
+          <t>-33,31; 12,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,29; -15,8</t>
+          <t>-55,56; -14,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 12,04</t>
+          <t>-22,85; 11,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,57; -28,8</t>
+          <t>-57,03; -29,17</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 12,7</t>
+          <t>-3,19; 13,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,48; -3,63</t>
+          <t>-18,21; -3,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 4,64</t>
+          <t>-11,32; 5,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 2,27</t>
+          <t>-16,01; 2,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 6,33</t>
+          <t>-4,75; 7,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,39; -3,84</t>
+          <t>-14,92; -1,98</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 56,03</t>
+          <t>-10,51; 56,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,58; -15,79</t>
+          <t>-60,29; -16,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 17,52</t>
+          <t>-33,16; 21,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 8,69</t>
+          <t>-47,84; 11,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 23,97</t>
+          <t>-15,09; 26,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,79; -13,91</t>
+          <t>-48,21; -6,8</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,48</t>
+          <t>-0,24; 7,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -8,25</t>
+          <t>-16,09; -8,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,21</t>
+          <t>-6,91; 0,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -6,18</t>
+          <t>-15,14; -6,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,76</t>
+          <t>-2,72; 3,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,56; -8,41</t>
+          <t>-14,37; -8,38</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 28,47</t>
+          <t>-0,83; 28,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,7; -31,48</t>
+          <t>-54,03; -31,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 4,44</t>
+          <t>-20,7; 2,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,99; -20,81</t>
+          <t>-45,05; -19,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 9,69</t>
+          <t>-8,36; 10,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,38; -28,57</t>
+          <t>-46,02; -28,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Edad-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 6,07</t>
+          <t>-11,34; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,01; -0,31</t>
+          <t>-19,79; -1,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -0,7</t>
+          <t>-19,12; -0,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,74; -3,19</t>
+          <t>-24,1; -1,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 0,52</t>
+          <t>-13,04; -0,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,53; -4,75</t>
+          <t>-19,32; -4,54</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 24,02</t>
+          <t>-34,92; 26,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,38; -0,47</t>
+          <t>-63,53; -4,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,54; -2,55</t>
+          <t>-44,47; -0,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,45; -8,03</t>
+          <t>-57,08; -1,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 1,45</t>
+          <t>-35,45; -1,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,13; -15,37</t>
+          <t>-54,12; -13,88</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 17,09</t>
+          <t>3,07; 17,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,0; -3,38</t>
+          <t>-17,3; -3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 8,47</t>
+          <t>-4,6; 7,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,71; -3,3</t>
+          <t>-16,64; -2,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 10,07</t>
+          <t>0,32; 10,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -5,44</t>
+          <t>-14,8; -5,5</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 71,85</t>
+          <t>9,34; 73,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,73; -14,04</t>
+          <t>-57,24; -13,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 36,05</t>
+          <t>-15,76; 31,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,51; -12,3</t>
+          <t>-56,59; -13,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 41,69</t>
+          <t>1,13; 40,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,28; -21,66</t>
+          <t>-51,28; -21,5</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 6,76</t>
+          <t>-9,13; 7,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,74; -8,9</t>
+          <t>-24,37; -8,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 3,69</t>
+          <t>-11,49; 4,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -4,23</t>
+          <t>-20,33; -5,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 3,17</t>
+          <t>-8,4; 2,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,21; -8,65</t>
+          <t>-19,96; -8,52</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 26,57</t>
+          <t>-25,89; 29,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,45; -31,23</t>
+          <t>-68,72; -31,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 12,65</t>
+          <t>-30,17; 16,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,56; -14,77</t>
+          <t>-55,16; -17,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 11,51</t>
+          <t>-23,87; 10,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,03; -29,17</t>
+          <t>-56,47; -28,15</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 13,03</t>
+          <t>-3,04; 13,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,21; -3,52</t>
+          <t>-18,95; -3,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 5,38</t>
+          <t>-10,96; 5,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 2,63</t>
+          <t>-16,64; 2,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 7,04</t>
+          <t>-4,82; 6,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,92; -1,98</t>
+          <t>-15,24; -3,18</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 56,9</t>
+          <t>-9,91; 57,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,29; -16,54</t>
+          <t>-60,07; -15,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 21,15</t>
+          <t>-31,91; 20,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 11,26</t>
+          <t>-49,88; 11,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 26,58</t>
+          <t>-15,4; 26,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,21; -6,8</t>
+          <t>-49,2; -10,64</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,45</t>
+          <t>-0,14; 7,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -8,42</t>
+          <t>-15,94; -8,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,73</t>
+          <t>-6,62; 1,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -6,16</t>
+          <t>-15,12; -5,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,0</t>
+          <t>-2,53; 2,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -8,38</t>
+          <t>-14,51; -8,19</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 28,96</t>
+          <t>-0,58; 28,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,03; -31,62</t>
+          <t>-53,43; -30,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 2,62</t>
+          <t>-19,59; 3,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,05; -19,29</t>
+          <t>-45,81; -18,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 10,43</t>
+          <t>-8,09; 9,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,02; -28,45</t>
+          <t>-46,63; -28,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Edad-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-10,08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-15,82</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-2,79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-11,15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,08</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-14,06</t>
+          <t>-11,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,49</t>
+          <t>-13,51</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 6,32</t>
+          <t>-19,27; -0,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,79; -1,64</t>
+          <t>-27,03; -4,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,12; -0,19</t>
+          <t>-11,64; 5,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,1; -1,25</t>
+          <t>-20,54; -1,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; -0,35</t>
+          <t>-13,03; -0,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,32; -4,54</t>
+          <t>-20,62; -5,51</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-25,95%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-40,74%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-9,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-39,71%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-25,95%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-36,2%</t>
+          <t>-39,43%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-37,32%</t>
+          <t>-40,35%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 26,62</t>
+          <t>-43,98; 0,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,53; -4,68</t>
+          <t>-62,87; -11,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,47; -0,36</t>
+          <t>-35,86; 23,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,08; -1,35</t>
+          <t>-66,01; -4,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,45; -1,5</t>
+          <t>-34,94; -0,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,12; -13,88</t>
+          <t>-57,24; -17,17</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-9,64</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>9,92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-10,41</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,33</t>
+          <t>-10,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-10,37</t>
+          <t>-9,93</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 17,36</t>
+          <t>-5,78; 7,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,3; -3,35</t>
+          <t>-16,13; -2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 7,44</t>
+          <t>2,98; 16,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,64; -2,99</t>
+          <t>-16,22; -2,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 10,07</t>
+          <t>0,27; 9,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,8; -5,5</t>
+          <t>-14,69; -4,68</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-35,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>36,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-38,06%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-37,83%</t>
+          <t>-37,43%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-37,94%</t>
+          <t>-36,33%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 73,44</t>
+          <t>-18,97; 30,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,24; -13,53</t>
+          <t>-54,44; -8,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 31,22</t>
+          <t>9,95; 70,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,59; -13,4</t>
+          <t>-54,3; -11,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 40,23</t>
+          <t>0,7; 39,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,28; -21,5</t>
+          <t>-49,4; -19,24</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-13,21</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-16,14</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,92</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-13,03</t>
+          <t>-15,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-14,3</t>
+          <t>-14,41</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 7,62</t>
+          <t>-11,54; 5,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,37; -8,94</t>
+          <t>-21,47; -4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 4,51</t>
+          <t>-9,72; 7,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -5,28</t>
+          <t>-24,14; -8,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 2,99</t>
+          <t>-8,77; 3,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,96; -8,52</t>
+          <t>-19,99; -8,04</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-11,64%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-39,28%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-3,18%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-52,28%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-11,64%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-38,72%</t>
+          <t>-51,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-44,34%</t>
+          <t>-44,65%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 29,95</t>
+          <t>-31,3; 15,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,72; -31,03</t>
+          <t>-56,51; -15,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 16,21</t>
+          <t>-27,16; 31,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,16; -17,45</t>
+          <t>-67,65; -30,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 10,0</t>
+          <t>-23,99; 12,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,47; -28,15</t>
+          <t>-57,17; -28,67</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-8,72</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>5,16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-10,69</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,31</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-8,75</t>
+          <t>-8,78</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,62</t>
+          <t>-8,67</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 13,28</t>
+          <t>-11,89; 4,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -3,67</t>
+          <t>-16,11; 1,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 5,39</t>
+          <t>-3,26; 12,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 2,98</t>
+          <t>-15,68; -1,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 6,84</t>
+          <t>-4,86; 6,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -3,18</t>
+          <t>-14,04; -3,22</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-10,85%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-28,53%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-39,42%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-10,85%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-28,62%</t>
+          <t>-32,37%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,3%</t>
+          <t>-30,03%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 57,33</t>
+          <t>-32,92; 17,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,07; -15,01</t>
+          <t>-47,88; 5,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 20,48</t>
+          <t>-10,66; 56,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 11,74</t>
+          <t>-51,43; -8,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 26,01</t>
+          <t>-15,2; 23,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,2; -10,64</t>
+          <t>-44,98; -10,53</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,99</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-11,06</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>3,59</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-12,07</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-11,08</t>
+          <t>-11,22</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-11,48</t>
+          <t>-11,1</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,37</t>
+          <t>-6,67; 1,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -8,09</t>
+          <t>-15,22; -6,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 1,11</t>
+          <t>-0,71; 7,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -5,85</t>
+          <t>-14,84; -7,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,63</t>
+          <t>-2,75; 2,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -8,19</t>
+          <t>-14,19; -8,1</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-9,45%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-34,95%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>12,71%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-42,77%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-9,45%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-35,03%</t>
+          <t>-39,77%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-38,29%</t>
+          <t>-37,01%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 28,14</t>
+          <t>-19,87; 4,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,43; -30,32</t>
+          <t>-46,0; -21,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 3,8</t>
+          <t>-2,4; 28,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -18,96</t>
+          <t>-49,41; -28,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 9,33</t>
+          <t>-8,71; 9,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,63; -28,51</t>
+          <t>-44,93; -27,99</t>
         </is>
       </c>
     </row>
